--- a/data/trans_camb/KIDM_A_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/KIDM_A_R-Edad-trans_camb.xlsx
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -614,7 +614,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>8-11</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -624,47 +624,47 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0,78</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0,13</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1,86</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1,81</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0,57</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-1,26</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1,29</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0,27</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0,12</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,34; 3,5</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,53; 2,24</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,34; 7,32</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,82; 5,67</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-4,14; 2,2</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-4,46; 2,08</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-0,98; 3,85</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,65; 1,69</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,09; 2,97</t>
         </is>
       </c>
     </row>
@@ -730,47 +730,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>55,97%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>134,29%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>62,75%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-19,63%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-43,48%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>59,4%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-12,44%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,33%</t>
         </is>
       </c>
     </row>
@@ -798,39 +798,39 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-47,42; 411,63</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-85,9; 195,3</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 412,05</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-44,05; 377,03</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-70,96; 198,09</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-75,89; 264,03</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>3-7</t>
+          <t>12-15</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -840,47 +840,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1,52</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-1,01</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-2,33</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1,51</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0,11</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0,06</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1,5</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0,56</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-1,14</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,76; 4,95</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-3,71; 1,42</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-5,11; -0,73</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-0,43; 4,64</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,94; 2,14</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,88; 2,05</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-0,31; 3,6</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,0; 1,1</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,72; 0,17</t>
         </is>
       </c>
     </row>
@@ -946,47 +946,47 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>57,84%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-38,63%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-88,88%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>127,86%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-9,11%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-5,13%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>79,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-29,42%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-60,45%</t>
         </is>
       </c>
     </row>
@@ -999,54 +999,54 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>-53,16; 355,39</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>-100,0; 18,13</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>-50,95; —</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-18,63; 328,35</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-79,39; 121,0</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-94,3; 37,23</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>8-11</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1056,47 +1056,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0,78</t>
+          <t>1,05</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0,13</t>
+          <t>-0,59</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1,86</t>
+          <t>-0,89</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,81</t>
+          <t>1,78</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>-0,57</t>
+          <t>-0,16</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-1,26</t>
+          <t>-0,56</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1,29</t>
+          <t>1,43</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-0,27</t>
+          <t>-0,37</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,12</t>
+          <t>-0,72</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 3,41</t>
+          <t>-1,15; 3,3</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 2,26</t>
+          <t>-2,56; 1,04</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 7,24</t>
+          <t>-2,67; 1,22</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 5,54</t>
+          <t>-0,22; 3,89</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,35; 2,34</t>
+          <t>-2,01; 1,77</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,41; 2,1</t>
+          <t>-2,49; 1,12</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 3,6</t>
+          <t>-0,36; 2,82</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 1,66</t>
+          <t>-1,65; 0,77</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 2,91</t>
+          <t>-1,92; 0,57</t>
         </is>
       </c>
     </row>
@@ -1162,47 +1162,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>55,97%</t>
+          <t>48,82%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>-27,49%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>134,29%</t>
+          <t>-41,63%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>62,75%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>-19,63%</t>
+          <t>-8,77%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-43,48%</t>
+          <t>-29,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>59,4%</t>
+          <t>71,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-12,44%</t>
+          <t>-18,59%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>-35,87%</t>
         </is>
       </c>
     </row>
@@ -1215,500 +1215,66 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-42,2; 280,88</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>-74,92; 100,41</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-88,86; 122,43</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-45,42; 468,97</t>
+          <t>-20,01; 369,77</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-74,79; 189,86</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 338,43</t>
+          <t>-86,81; 121,92</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-41,83; 310,04</t>
+          <t>-14,0; 210,43</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-69,57; 161,92</t>
+          <t>-60,39; 56,47</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-80,92; 306,74</t>
+          <t>-75,98; 49,9</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>12-15</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Cambio absoluto (puntos porcentuales)</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>1,52</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>-1,01</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-2,33</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1,51</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-0,11</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>-0,06</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>1,5</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>-0,56</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>-1,14</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="n"/>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>-1,57; 4,98</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>-3,52; 1,44</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>-4,54; -0,46</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>-0,65; 4,02</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>-1,99; 2,04</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-1,76; 2,16</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>-0,45; 3,86</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>-2,1; 1,08</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>-2,54; 0,48</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="n"/>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>57,84%</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>-38,63%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-88,88%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>127,86%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-9,11%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>-5,13%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>79,53%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>-29,42%</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>-60,45%</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="n"/>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>-48,72; 382,12</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>-89,54; 116,63</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 50,85</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>-51,52; 985,13</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>-21,15; 341,63</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>-76,44; 110,37</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>-92,42; 102,53</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>Cambio absoluto (puntos porcentuales)</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>1,05</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>-0,59</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-0,89</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>1,78</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-0,16</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>-0,56</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>1,43</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>-0,37</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>-0,72</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="n"/>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>-1,09; 3,4</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>-2,38; 1,09</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>-3,01; 1,02</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>-0,13; 4,19</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>-1,9; 1,78</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>-2,4; 1,24</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>0,03; 3,07</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>-1,51; 0,94</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>-2,0; 0,49</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="n"/>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>48,82%</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>-27,49%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-41,63%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>95,51%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-8,77%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>-29,91%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>71,27%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>-18,59%</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>-35,87%</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n"/>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>-36,98; 264,52</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>-77,52; 113,65</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>-90,22; 93,39</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>-17,51; 420,69</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>-70,92; 220,32</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>-86,42; 183,21</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>-4,07; 215,25</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>-59,17; 83,19</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>-75,45; 39,03</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="7">
     <mergeCell ref="A4:A7"/>
     <mergeCell ref="C1:E1"/>
     <mergeCell ref="A8:A11"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="A12:A15"/>
     <mergeCell ref="I1:K1"/>
-    <mergeCell ref="A20:A23"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A16:A19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/trans_camb/KIDM_A_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/KIDM_A_R-Edad-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores con salud general autopercibida regular o mala (autopercepción menor)</t>
+          <t>Menores cuya salud general autopercibida es regular o mala</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 3,5</t>
+          <t>-2,18; 3,7</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 2,24</t>
+          <t>-2,75; 2,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 7,32</t>
+          <t>-1,45; 6,77</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 5,67</t>
+          <t>-2,06; 5,76</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,14; 2,2</t>
+          <t>-3,94; 2,45</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-4,46; 2,08</t>
+          <t>-4,23; 2,22</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 3,85</t>
+          <t>-1,04; 3,72</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 1,69</t>
+          <t>-2,58; 1,73</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 2,97</t>
+          <t>-2,26; 2,94</t>
         </is>
       </c>
     </row>
@@ -798,32 +798,32 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-47,42; 411,63</t>
+          <t>-48,74; 455,69</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-85,9; 195,3</t>
+          <t>-87,13; 265,91</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 412,05</t>
+          <t>-100,0; 314,78</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-44,05; 377,03</t>
+          <t>-38,52; 391,57</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-70,96; 198,09</t>
+          <t>-72,04; 194,65</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-75,89; 264,03</t>
+          <t>-78,06; 253,25</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 4,95</t>
+          <t>-1,29; 5,07</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 1,42</t>
+          <t>-3,59; 1,29</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,11; -0,73</t>
+          <t>-5,01; -0,65</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 4,64</t>
+          <t>-0,68; 4,23</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 2,14</t>
+          <t>-1,67; 2,25</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 2,05</t>
+          <t>-1,85; 2,06</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 3,6</t>
+          <t>-0,38; 3,69</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 1,1</t>
+          <t>-2,15; 1,15</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 0,17</t>
+          <t>-2,58; 0,21</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-53,16; 355,39</t>
+          <t>-40,65; 367,94</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>-88,16; 100,47</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>-100,0; 40,52</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>-58,0; 1392,68</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 18,13</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-50,95; —</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-18,63; 328,35</t>
+          <t>-21,47; 346,18</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-79,39; 121,0</t>
+          <t>-79,31; 130,58</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-94,3; 37,23</t>
+          <t>-92,11; 58,0</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 3,3</t>
+          <t>-1,03; 3,48</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 1,04</t>
+          <t>-2,4; 1,22</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,67; 1,22</t>
+          <t>-2,77; 1,23</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 3,89</t>
+          <t>-0,22; 3,98</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 1,77</t>
+          <t>-1,9; 1,6</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 1,12</t>
+          <t>-2,25; 1,19</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 2,82</t>
+          <t>-0,08; 2,95</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 0,77</t>
+          <t>-1,68; 0,77</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 0,57</t>
+          <t>-2,02; 0,67</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-42,2; 280,88</t>
+          <t>-41,45; 287,61</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-74,92; 100,41</t>
+          <t>-74,76; 133,29</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-88,86; 122,43</t>
+          <t>-89,07; 125,78</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-20,01; 369,77</t>
+          <t>-19,03; 373,53</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-74,79; 189,86</t>
+          <t>-72,48; 189,85</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-86,81; 121,92</t>
+          <t>-86,14; 146,26</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-14,0; 210,43</t>
+          <t>-2,95; 227,77</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-60,39; 56,47</t>
+          <t>-60,27; 65,01</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-75,98; 49,9</t>
+          <t>-76,49; 58,66</t>
         </is>
       </c>
     </row>
